--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python 封裝\封裝20260330\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578FB946-84E8-49E9-9528-FA7EBDD0873E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020"/>
+    <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{373C416E-3089-4CE1-B757-7C7D79C28350}"/>
   </bookViews>
   <sheets>
     <sheet name="股東大會贈品" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -2563,8 +2569,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="19">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3255,7 +3261,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -3307,7 +3313,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -3521,18 +3527,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBBAC253-DA3E-40C2-AB28-54D101D79F7C}">
   <dimension ref="A1:K398"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3567,7 +3573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>15011</v>
       </c>
@@ -3593,7 +3599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>15013</v>
       </c>
@@ -3619,7 +3625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>15012</v>
       </c>
@@ -3645,7 +3651,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>15014</v>
       </c>
@@ -3671,7 +3677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F6" t="s">
         <v>18</v>
       </c>
@@ -3684,8 +3690,11 @@
       <c r="I6">
         <v>1101</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="J6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F7" t="s">
         <v>21</v>
       </c>
@@ -3698,8 +3707,11 @@
       <c r="I7">
         <v>1103</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="J7">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F8" t="s">
         <v>24</v>
       </c>
@@ -3712,8 +3724,11 @@
       <c r="I8">
         <v>1210</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="J8">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F9" t="s">
         <v>18</v>
       </c>
@@ -3727,7 +3742,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F10" t="s">
         <v>29</v>
       </c>
@@ -3741,7 +3756,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F11" t="s">
         <v>32</v>
       </c>
@@ -3755,7 +3770,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F12" t="s">
         <v>35</v>
       </c>
@@ -3769,7 +3784,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F13" t="s">
         <v>38</v>
       </c>
@@ -3783,7 +3798,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F14" t="s">
         <v>35</v>
       </c>
@@ -3797,7 +3812,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F15" t="s">
         <v>18</v>
       </c>
@@ -3811,7 +3826,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="F16" t="s">
         <v>45</v>
       </c>
@@ -3825,7 +3840,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="17" spans="6:9">
+    <row r="17" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F17" t="s">
         <v>48</v>
       </c>
@@ -3839,7 +3854,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="18" spans="6:9">
+    <row r="18" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F18" t="s">
         <v>51</v>
       </c>
@@ -3853,7 +3868,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="19" spans="6:9">
+    <row r="19" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F19" t="s">
         <v>32</v>
       </c>
@@ -3867,7 +3882,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="20" spans="6:9">
+    <row r="20" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F20" t="s">
         <v>56</v>
       </c>
@@ -3881,7 +3896,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="21" spans="6:9">
+    <row r="21" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F21" t="s">
         <v>51</v>
       </c>
@@ -3895,7 +3910,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="22" spans="6:9">
+    <row r="22" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F22" t="s">
         <v>29</v>
       </c>
@@ -3909,7 +3924,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="23" spans="6:9">
+    <row r="23" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F23" t="s">
         <v>63</v>
       </c>
@@ -3923,7 +3938,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="24" spans="6:9">
+    <row r="24" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F24" t="s">
         <v>32</v>
       </c>
@@ -3937,7 +3952,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="25" spans="6:9">
+    <row r="25" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F25" t="s">
         <v>68</v>
       </c>
@@ -3951,7 +3966,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="26" spans="6:9">
+    <row r="26" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F26" t="s">
         <v>48</v>
       </c>
@@ -3965,7 +3980,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="27" spans="6:9">
+    <row r="27" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F27" t="s">
         <v>38</v>
       </c>
@@ -3979,7 +3994,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="28" spans="6:9">
+    <row r="28" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F28" t="s">
         <v>21</v>
       </c>
@@ -3993,7 +4008,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="29" spans="6:9">
+    <row r="29" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F29" t="s">
         <v>18</v>
       </c>
@@ -4007,7 +4022,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="30" spans="6:9">
+    <row r="30" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F30" t="s">
         <v>79</v>
       </c>
@@ -4021,7 +4036,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="31" spans="6:9">
+    <row r="31" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F31" t="s">
         <v>82</v>
       </c>
@@ -4035,7 +4050,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="32" spans="6:9">
+    <row r="32" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F32" t="s">
         <v>18</v>
       </c>
@@ -4049,7 +4064,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="33" spans="6:9">
+    <row r="33" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F33" t="s">
         <v>79</v>
       </c>
@@ -4063,7 +4078,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="34" spans="6:9">
+    <row r="34" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F34" t="s">
         <v>38</v>
       </c>
@@ -4077,7 +4092,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="35" spans="6:9">
+    <row r="35" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F35" t="s">
         <v>32</v>
       </c>
@@ -4091,7 +4106,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="36" spans="6:9">
+    <row r="36" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F36" t="s">
         <v>38</v>
       </c>
@@ -4105,7 +4120,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="37" spans="6:9">
+    <row r="37" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F37" t="s">
         <v>32</v>
       </c>
@@ -4119,7 +4134,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="38" spans="6:9">
+    <row r="38" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F38" t="s">
         <v>38</v>
       </c>
@@ -4133,7 +4148,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="39" spans="6:9">
+    <row r="39" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F39" t="s">
         <v>99</v>
       </c>
@@ -4147,7 +4162,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="40" spans="6:9">
+    <row r="40" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F40" t="s">
         <v>82</v>
       </c>
@@ -4161,7 +4176,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="41" spans="6:9">
+    <row r="41" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F41" t="s">
         <v>48</v>
       </c>
@@ -4175,7 +4190,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="42" spans="6:9">
+    <row r="42" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F42" t="s">
         <v>48</v>
       </c>
@@ -4189,7 +4204,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="43" spans="6:9">
+    <row r="43" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F43" t="s">
         <v>29</v>
       </c>
@@ -4203,7 +4218,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="44" spans="6:9">
+    <row r="44" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F44" t="s">
         <v>32</v>
       </c>
@@ -4217,7 +4232,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="45" spans="6:9">
+    <row r="45" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F45" t="s">
         <v>112</v>
       </c>
@@ -4231,7 +4246,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="46" spans="6:9">
+    <row r="46" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F46" t="s">
         <v>82</v>
       </c>
@@ -4245,7 +4260,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="47" spans="6:9">
+    <row r="47" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F47" t="s">
         <v>117</v>
       </c>
@@ -4259,7 +4274,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="48" spans="6:9">
+    <row r="48" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F48" t="s">
         <v>32</v>
       </c>
@@ -4273,7 +4288,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="49" spans="6:9">
+    <row r="49" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F49" t="s">
         <v>24</v>
       </c>
@@ -4287,7 +4302,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="50" spans="6:9">
+    <row r="50" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F50" t="s">
         <v>124</v>
       </c>
@@ -4301,7 +4316,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="51" spans="6:9">
+    <row r="51" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F51" t="s">
         <v>127</v>
       </c>
@@ -4315,7 +4330,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="52" spans="6:9">
+    <row r="52" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F52" t="s">
         <v>21</v>
       </c>
@@ -4329,7 +4344,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="6:9">
+    <row r="53" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F53" t="s">
         <v>82</v>
       </c>
@@ -4343,7 +4358,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="6:9">
+    <row r="54" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F54" t="s">
         <v>32</v>
       </c>
@@ -4357,7 +4372,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="55" spans="6:9">
+    <row r="55" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F55" t="s">
         <v>136</v>
       </c>
@@ -4371,7 +4386,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="56" spans="6:9">
+    <row r="56" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F56" t="s">
         <v>35</v>
       </c>
@@ -4385,7 +4400,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="57" spans="6:9">
+    <row r="57" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F57" t="s">
         <v>141</v>
       </c>
@@ -4399,7 +4414,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="58" spans="6:9">
+    <row r="58" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F58" t="s">
         <v>144</v>
       </c>
@@ -4413,7 +4428,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="59" spans="6:9">
+    <row r="59" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F59" t="s">
         <v>21</v>
       </c>
@@ -4427,7 +4442,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="60" spans="6:9">
+    <row r="60" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F60" t="s">
         <v>18</v>
       </c>
@@ -4441,7 +4456,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="61" spans="6:9">
+    <row r="61" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F61" t="s">
         <v>151</v>
       </c>
@@ -4455,7 +4470,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="62" spans="6:9">
+    <row r="62" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F62" t="s">
         <v>35</v>
       </c>
@@ -4469,7 +4484,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="63" spans="6:9">
+    <row r="63" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F63" t="s">
         <v>156</v>
       </c>
@@ -4483,7 +4498,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="64" spans="6:9">
+    <row r="64" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F64" t="s">
         <v>144</v>
       </c>
@@ -4497,7 +4512,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="65" spans="6:9">
+    <row r="65" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F65" t="s">
         <v>35</v>
       </c>
@@ -4511,7 +4526,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="66" spans="6:9">
+    <row r="66" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F66" t="s">
         <v>18</v>
       </c>
@@ -4525,7 +4540,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="67" spans="6:9">
+    <row r="67" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F67" t="s">
         <v>127</v>
       </c>
@@ -4539,7 +4554,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="68" spans="6:9">
+    <row r="68" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F68" t="s">
         <v>156</v>
       </c>
@@ -4553,7 +4568,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="69" spans="6:9">
+    <row r="69" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F69" t="s">
         <v>32</v>
       </c>
@@ -4567,7 +4582,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="70" spans="6:9">
+    <row r="70" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F70" t="s">
         <v>63</v>
       </c>
@@ -4581,7 +4596,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="71" spans="6:9">
+    <row r="71" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F71" t="s">
         <v>156</v>
       </c>
@@ -4595,7 +4610,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="72" spans="6:9">
+    <row r="72" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F72" t="s">
         <v>38</v>
       </c>
@@ -4609,7 +4624,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="73" spans="6:9">
+    <row r="73" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F73" t="s">
         <v>38</v>
       </c>
@@ -4623,7 +4638,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="74" spans="6:9">
+    <row r="74" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F74" t="s">
         <v>179</v>
       </c>
@@ -4637,7 +4652,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="75" spans="6:9">
+    <row r="75" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F75" t="s">
         <v>182</v>
       </c>
@@ -4651,7 +4666,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="76" spans="6:9">
+    <row r="76" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F76" t="s">
         <v>182</v>
       </c>
@@ -4665,7 +4680,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="77" spans="6:9">
+    <row r="77" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F77" t="s">
         <v>56</v>
       </c>
@@ -4679,7 +4694,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="78" spans="6:9">
+    <row r="78" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F78" t="s">
         <v>187</v>
       </c>
@@ -4693,7 +4708,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="79" spans="6:9">
+    <row r="79" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F79" t="s">
         <v>24</v>
       </c>
@@ -4707,7 +4722,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="80" spans="6:9">
+    <row r="80" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F80" t="s">
         <v>82</v>
       </c>
@@ -4721,7 +4736,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="81" spans="6:9">
+    <row r="81" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F81" t="s">
         <v>179</v>
       </c>
@@ -4735,7 +4750,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="82" spans="6:9">
+    <row r="82" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F82" t="s">
         <v>56</v>
       </c>
@@ -4749,7 +4764,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="83" spans="6:9">
+    <row r="83" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F83" t="s">
         <v>198</v>
       </c>
@@ -4763,7 +4778,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="84" spans="6:9">
+    <row r="84" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F84" t="s">
         <v>56</v>
       </c>
@@ -4777,7 +4792,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="85" spans="6:9">
+    <row r="85" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F85" t="s">
         <v>38</v>
       </c>
@@ -4791,7 +4806,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="86" spans="6:9">
+    <row r="86" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F86" t="s">
         <v>21</v>
       </c>
@@ -4805,7 +4820,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="87" spans="6:9">
+    <row r="87" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F87" t="s">
         <v>207</v>
       </c>
@@ -4819,7 +4834,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="88" spans="6:9">
+    <row r="88" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F88" t="s">
         <v>187</v>
       </c>
@@ -4833,7 +4848,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="89" spans="6:9">
+    <row r="89" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F89" t="s">
         <v>212</v>
       </c>
@@ -4847,7 +4862,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="90" spans="6:9">
+    <row r="90" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F90" t="s">
         <v>38</v>
       </c>
@@ -4861,7 +4876,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="91" spans="6:9">
+    <row r="91" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F91" t="s">
         <v>38</v>
       </c>
@@ -4875,7 +4890,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="92" spans="6:9">
+    <row r="92" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F92" t="s">
         <v>179</v>
       </c>
@@ -4889,7 +4904,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="93" spans="6:9">
+    <row r="93" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F93" t="s">
         <v>112</v>
       </c>
@@ -4903,7 +4918,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="94" spans="6:9">
+    <row r="94" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F94" t="s">
         <v>127</v>
       </c>
@@ -4917,7 +4932,7 @@
         <v>2464</v>
       </c>
     </row>
-    <row r="95" spans="6:9">
+    <row r="95" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F95" t="s">
         <v>182</v>
       </c>
@@ -4931,7 +4946,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="96" spans="6:9">
+    <row r="96" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F96" t="s">
         <v>79</v>
       </c>
@@ -4945,7 +4960,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="97" spans="6:9">
+    <row r="97" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F97" t="s">
         <v>187</v>
       </c>
@@ -4959,7 +4974,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="98" spans="6:9">
+    <row r="98" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F98" t="s">
         <v>38</v>
       </c>
@@ -4973,7 +4988,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="99" spans="6:9">
+    <row r="99" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F99" t="s">
         <v>117</v>
       </c>
@@ -4987,7 +5002,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="100" spans="6:9">
+    <row r="100" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F100" t="s">
         <v>56</v>
       </c>
@@ -5001,7 +5016,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="101" spans="6:9">
+    <row r="101" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F101" t="s">
         <v>237</v>
       </c>
@@ -5015,7 +5030,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="102" spans="6:9">
+    <row r="102" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F102" t="s">
         <v>35</v>
       </c>
@@ -5029,7 +5044,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="103" spans="6:9">
+    <row r="103" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F103" t="s">
         <v>18</v>
       </c>
@@ -5043,7 +5058,7 @@
         <v>2506</v>
       </c>
     </row>
-    <row r="104" spans="6:9">
+    <row r="104" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F104" t="s">
         <v>82</v>
       </c>
@@ -5057,7 +5072,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="105" spans="6:9">
+    <row r="105" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F105" t="s">
         <v>38</v>
       </c>
@@ -5071,7 +5086,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="106" spans="6:9">
+    <row r="106" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F106" t="s">
         <v>35</v>
       </c>
@@ -5085,7 +5100,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="107" spans="6:9">
+    <row r="107" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F107" t="s">
         <v>79</v>
       </c>
@@ -5099,7 +5114,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="108" spans="6:9">
+    <row r="108" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F108" t="s">
         <v>35</v>
       </c>
@@ -5113,7 +5128,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="109" spans="6:9">
+    <row r="109" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F109" t="s">
         <v>117</v>
       </c>
@@ -5127,7 +5142,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="110" spans="6:9">
+    <row r="110" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F110" t="s">
         <v>56</v>
       </c>
@@ -5141,7 +5156,7 @@
         <v>2601</v>
       </c>
     </row>
-    <row r="111" spans="6:9">
+    <row r="111" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F111" t="s">
         <v>51</v>
       </c>
@@ -5155,7 +5170,7 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="112" spans="6:9">
+    <row r="112" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F112" t="s">
         <v>38</v>
       </c>
@@ -5169,7 +5184,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="113" spans="6:9">
+    <row r="113" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F113" t="s">
         <v>82</v>
       </c>
@@ -5183,7 +5198,7 @@
         <v>2612</v>
       </c>
     </row>
-    <row r="114" spans="6:9">
+    <row r="114" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F114" t="s">
         <v>82</v>
       </c>
@@ -5197,7 +5212,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="115" spans="6:9">
+    <row r="115" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F115" t="s">
         <v>79</v>
       </c>
@@ -5211,7 +5226,7 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="116" spans="6:9">
+    <row r="116" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F116" t="s">
         <v>156</v>
       </c>
@@ -5225,7 +5240,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="117" spans="6:9">
+    <row r="117" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F117" t="s">
         <v>18</v>
       </c>
@@ -5239,7 +5254,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="118" spans="6:9">
+    <row r="118" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F118" t="s">
         <v>32</v>
       </c>
@@ -5253,7 +5268,7 @@
         <v>2641</v>
       </c>
     </row>
-    <row r="119" spans="6:9">
+    <row r="119" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F119" t="s">
         <v>187</v>
       </c>
@@ -5267,7 +5282,7 @@
         <v>2705</v>
       </c>
     </row>
-    <row r="120" spans="6:9">
+    <row r="120" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F120" t="s">
         <v>16</v>
       </c>
@@ -5281,7 +5296,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="121" spans="6:9">
+    <row r="121" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F121" t="s">
         <v>56</v>
       </c>
@@ -5295,7 +5310,7 @@
         <v>2885</v>
       </c>
     </row>
-    <row r="122" spans="6:9">
+    <row r="122" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F122" t="s">
         <v>32</v>
       </c>
@@ -5309,7 +5324,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="123" spans="6:9">
+    <row r="123" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F123" t="s">
         <v>151</v>
       </c>
@@ -5323,7 +5338,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="124" spans="6:9">
+    <row r="124" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F124" t="s">
         <v>45</v>
       </c>
@@ -5337,7 +5352,7 @@
         <v>3006</v>
       </c>
     </row>
-    <row r="125" spans="6:9">
+    <row r="125" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F125" t="s">
         <v>156</v>
       </c>
@@ -5351,7 +5366,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="126" spans="6:9">
+    <row r="126" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F126" t="s">
         <v>187</v>
       </c>
@@ -5365,7 +5380,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="127" spans="6:9">
+    <row r="127" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F127" t="s">
         <v>144</v>
       </c>
@@ -5379,7 +5394,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="128" spans="6:9">
+    <row r="128" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F128" t="s">
         <v>38</v>
       </c>
@@ -5393,7 +5408,7 @@
         <v>3023</v>
       </c>
     </row>
-    <row r="129" spans="6:9">
+    <row r="129" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F129" t="s">
         <v>156</v>
       </c>
@@ -5407,7 +5422,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="130" spans="6:9">
+    <row r="130" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F130" t="s">
         <v>32</v>
       </c>
@@ -5421,7 +5436,7 @@
         <v>3028</v>
       </c>
     </row>
-    <row r="131" spans="6:9">
+    <row r="131" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F131" t="s">
         <v>187</v>
       </c>
@@ -5435,7 +5450,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="132" spans="6:9">
+    <row r="132" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F132" t="s">
         <v>187</v>
       </c>
@@ -5449,7 +5464,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="133" spans="6:9">
+    <row r="133" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F133" t="s">
         <v>212</v>
       </c>
@@ -5463,7 +5478,7 @@
         <v>3036</v>
       </c>
     </row>
-    <row r="134" spans="6:9">
+    <row r="134" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F134" t="s">
         <v>51</v>
       </c>
@@ -5477,7 +5492,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="135" spans="6:9">
+    <row r="135" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F135" t="s">
         <v>56</v>
       </c>
@@ -5491,7 +5506,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="136" spans="6:9">
+    <row r="136" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F136" t="s">
         <v>21</v>
       </c>
@@ -5505,7 +5520,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="137" spans="6:9">
+    <row r="137" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F137" t="s">
         <v>56</v>
       </c>
@@ -5519,7 +5534,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="138" spans="6:9">
+    <row r="138" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F138" t="s">
         <v>51</v>
       </c>
@@ -5533,7 +5548,7 @@
         <v>3057</v>
       </c>
     </row>
-    <row r="139" spans="6:9">
+    <row r="139" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F139" t="s">
         <v>48</v>
       </c>
@@ -5547,7 +5562,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="140" spans="6:9">
+    <row r="140" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F140" t="s">
         <v>21</v>
       </c>
@@ -5561,7 +5576,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="141" spans="6:9">
+    <row r="141" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F141" t="s">
         <v>187</v>
       </c>
@@ -5575,7 +5590,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="142" spans="6:9">
+    <row r="142" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F142" t="s">
         <v>63</v>
       </c>
@@ -5589,7 +5604,7 @@
         <v>3090</v>
       </c>
     </row>
-    <row r="143" spans="6:9">
+    <row r="143" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F143" t="s">
         <v>45</v>
       </c>
@@ -5603,7 +5618,7 @@
         <v>3095</v>
       </c>
     </row>
-    <row r="144" spans="6:9">
+    <row r="144" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F144" t="s">
         <v>212</v>
       </c>
@@ -5617,7 +5632,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="145" spans="6:9">
+    <row r="145" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F145" t="s">
         <v>112</v>
       </c>
@@ -5631,7 +5646,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="146" spans="6:9">
+    <row r="146" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F146" t="s">
         <v>48</v>
       </c>
@@ -5645,7 +5660,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="147" spans="6:9">
+    <row r="147" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F147" t="s">
         <v>144</v>
       </c>
@@ -5659,7 +5674,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="148" spans="6:9">
+    <row r="148" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F148" t="s">
         <v>45</v>
       </c>
@@ -5673,7 +5688,7 @@
         <v>3141</v>
       </c>
     </row>
-    <row r="149" spans="6:9">
+    <row r="149" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F149" t="s">
         <v>32</v>
       </c>
@@ -5687,7 +5702,7 @@
         <v>3149</v>
       </c>
     </row>
-    <row r="150" spans="6:9">
+    <row r="150" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F150" t="s">
         <v>99</v>
       </c>
@@ -5701,7 +5716,7 @@
         <v>3163</v>
       </c>
     </row>
-    <row r="151" spans="6:9">
+    <row r="151" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F151" t="s">
         <v>79</v>
       </c>
@@ -5715,7 +5730,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="152" spans="6:9">
+    <row r="152" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F152" t="s">
         <v>144</v>
       </c>
@@ -5729,7 +5744,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="153" spans="6:9">
+    <row r="153" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F153" t="s">
         <v>21</v>
       </c>
@@ -5743,7 +5758,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="154" spans="6:9">
+    <row r="154" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F154" t="s">
         <v>82</v>
       </c>
@@ -5757,7 +5772,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="155" spans="6:9">
+    <row r="155" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F155" t="s">
         <v>51</v>
       </c>
@@ -5771,7 +5786,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="156" spans="6:9">
+    <row r="156" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F156" t="s">
         <v>38</v>
       </c>
@@ -5785,7 +5800,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="157" spans="6:9">
+    <row r="157" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F157" t="s">
         <v>207</v>
       </c>
@@ -5799,7 +5814,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="158" spans="6:9">
+    <row r="158" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F158" t="s">
         <v>18</v>
       </c>
@@ -5813,7 +5828,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="159" spans="6:9">
+    <row r="159" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F159" t="s">
         <v>144</v>
       </c>
@@ -5827,7 +5842,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="160" spans="6:9">
+    <row r="160" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F160" t="s">
         <v>35</v>
       </c>
@@ -5841,7 +5856,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="161" spans="6:9">
+    <row r="161" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F161" t="s">
         <v>51</v>
       </c>
@@ -5855,7 +5870,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="162" spans="6:9">
+    <row r="162" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F162" t="s">
         <v>212</v>
       </c>
@@ -5869,7 +5884,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="163" spans="6:9">
+    <row r="163" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F163" t="s">
         <v>38</v>
       </c>
@@ -5883,7 +5898,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="164" spans="6:9">
+    <row r="164" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F164" t="s">
         <v>56</v>
       </c>
@@ -5897,7 +5912,7 @@
         <v>3289</v>
       </c>
     </row>
-    <row r="165" spans="6:9">
+    <row r="165" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F165" t="s">
         <v>79</v>
       </c>
@@ -5911,7 +5926,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="166" spans="6:9">
+    <row r="166" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F166" t="s">
         <v>24</v>
       </c>
@@ -5925,7 +5940,7 @@
         <v>3306</v>
       </c>
     </row>
-    <row r="167" spans="6:9">
+    <row r="167" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F167" t="s">
         <v>151</v>
       </c>
@@ -5939,7 +5954,7 @@
         <v>3317</v>
       </c>
     </row>
-    <row r="168" spans="6:9">
+    <row r="168" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F168" t="s">
         <v>18</v>
       </c>
@@ -5953,7 +5968,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="169" spans="6:9">
+    <row r="169" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F169" t="s">
         <v>21</v>
       </c>
@@ -5967,7 +5982,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="170" spans="6:9">
+    <row r="170" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F170" t="s">
         <v>45</v>
       </c>
@@ -5981,7 +5996,7 @@
         <v>3323</v>
       </c>
     </row>
-    <row r="171" spans="6:9">
+    <row r="171" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F171" t="s">
         <v>136</v>
       </c>
@@ -5995,7 +6010,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="172" spans="6:9">
+    <row r="172" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F172" t="s">
         <v>18</v>
       </c>
@@ -6009,7 +6024,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="173" spans="6:9">
+    <row r="173" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F173" t="s">
         <v>136</v>
       </c>
@@ -6023,7 +6038,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="174" spans="6:9">
+    <row r="174" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F174" t="s">
         <v>136</v>
       </c>
@@ -6037,7 +6052,7 @@
         <v>3363</v>
       </c>
     </row>
-    <row r="175" spans="6:9">
+    <row r="175" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F175" t="s">
         <v>24</v>
       </c>
@@ -6051,7 +6066,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="176" spans="6:9">
+    <row r="176" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F176" t="s">
         <v>38</v>
       </c>
@@ -6065,7 +6080,7 @@
         <v>3376</v>
       </c>
     </row>
-    <row r="177" spans="6:9">
+    <row r="177" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F177" t="s">
         <v>48</v>
       </c>
@@ -6079,7 +6094,7 @@
         <v>3402</v>
       </c>
     </row>
-    <row r="178" spans="6:9">
+    <row r="178" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F178" t="s">
         <v>51</v>
       </c>
@@ -6093,7 +6108,7 @@
         <v>3430</v>
       </c>
     </row>
-    <row r="179" spans="6:9">
+    <row r="179" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F179" t="s">
         <v>63</v>
       </c>
@@ -6107,7 +6122,7 @@
         <v>3437</v>
       </c>
     </row>
-    <row r="180" spans="6:9">
+    <row r="180" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F180" t="s">
         <v>187</v>
       </c>
@@ -6121,7 +6136,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="181" spans="6:9">
+    <row r="181" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F181" t="s">
         <v>187</v>
       </c>
@@ -6135,7 +6150,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="182" spans="6:9">
+    <row r="182" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F182" t="s">
         <v>51</v>
       </c>
@@ -6149,7 +6164,7 @@
         <v>3481</v>
       </c>
     </row>
-    <row r="183" spans="6:9">
+    <row r="183" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F183" t="s">
         <v>187</v>
       </c>
@@ -6163,7 +6178,7 @@
         <v>3483</v>
       </c>
     </row>
-    <row r="184" spans="6:9">
+    <row r="184" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F184" t="s">
         <v>79</v>
       </c>
@@ -6177,7 +6192,7 @@
         <v>3490</v>
       </c>
     </row>
-    <row r="185" spans="6:9">
+    <row r="185" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F185" t="s">
         <v>56</v>
       </c>
@@ -6191,7 +6206,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="186" spans="6:9">
+    <row r="186" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F186" t="s">
         <v>408</v>
       </c>
@@ -6205,7 +6220,7 @@
         <v>3518</v>
       </c>
     </row>
-    <row r="187" spans="6:9">
+    <row r="187" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F187" t="s">
         <v>56</v>
       </c>
@@ -6219,7 +6234,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="188" spans="6:9">
+    <row r="188" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F188" t="s">
         <v>21</v>
       </c>
@@ -6233,7 +6248,7 @@
         <v>3535</v>
       </c>
     </row>
-    <row r="189" spans="6:9">
+    <row r="189" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F189" t="s">
         <v>56</v>
       </c>
@@ -6247,7 +6262,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="190" spans="6:9">
+    <row r="190" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F190" t="s">
         <v>82</v>
       </c>
@@ -6261,7 +6276,7 @@
         <v>3543</v>
       </c>
     </row>
-    <row r="191" spans="6:9">
+    <row r="191" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F191" t="s">
         <v>79</v>
       </c>
@@ -6275,7 +6290,7 @@
         <v>3545</v>
       </c>
     </row>
-    <row r="192" spans="6:9">
+    <row r="192" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F192" t="s">
         <v>156</v>
       </c>
@@ -6289,7 +6304,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="193" spans="6:9">
+    <row r="193" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F193" t="s">
         <v>127</v>
       </c>
@@ -6303,7 +6318,7 @@
         <v>3563</v>
       </c>
     </row>
-    <row r="194" spans="6:9">
+    <row r="194" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F194" t="s">
         <v>56</v>
       </c>
@@ -6317,7 +6332,7 @@
         <v>3567</v>
       </c>
     </row>
-    <row r="195" spans="6:9">
+    <row r="195" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F195" t="s">
         <v>187</v>
       </c>
@@ -6331,7 +6346,7 @@
         <v>3576</v>
       </c>
     </row>
-    <row r="196" spans="6:9">
+    <row r="196" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F196" t="s">
         <v>144</v>
       </c>
@@ -6345,7 +6360,7 @@
         <v>3580</v>
       </c>
     </row>
-    <row r="197" spans="6:9">
+    <row r="197" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F197" t="s">
         <v>18</v>
       </c>
@@ -6359,7 +6374,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="198" spans="6:9">
+    <row r="198" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F198" t="s">
         <v>29</v>
       </c>
@@ -6373,7 +6388,7 @@
         <v>3624</v>
       </c>
     </row>
-    <row r="199" spans="6:9">
+    <row r="199" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F199" t="s">
         <v>24</v>
       </c>
@@ -6387,7 +6402,7 @@
         <v>3686</v>
       </c>
     </row>
-    <row r="200" spans="6:9">
+    <row r="200" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F200" t="s">
         <v>437</v>
       </c>
@@ -6401,7 +6416,7 @@
         <v>3687</v>
       </c>
     </row>
-    <row r="201" spans="6:9">
+    <row r="201" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F201" t="s">
         <v>144</v>
       </c>
@@ -6415,7 +6430,7 @@
         <v>3689</v>
       </c>
     </row>
-    <row r="202" spans="6:9">
+    <row r="202" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F202" t="s">
         <v>56</v>
       </c>
@@ -6429,7 +6444,7 @@
         <v>3712</v>
       </c>
     </row>
-    <row r="203" spans="6:9">
+    <row r="203" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F203" t="s">
         <v>198</v>
       </c>
@@ -6443,7 +6458,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="204" spans="6:9">
+    <row r="204" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F204" t="s">
         <v>79</v>
       </c>
@@ -6457,7 +6472,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="205" spans="6:9">
+    <row r="205" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F205" t="s">
         <v>82</v>
       </c>
@@ -6471,7 +6486,7 @@
         <v>3716</v>
       </c>
     </row>
-    <row r="206" spans="6:9">
+    <row r="206" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F206" t="s">
         <v>144</v>
       </c>
@@ -6485,7 +6500,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="207" spans="6:9">
+    <row r="207" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F207" t="s">
         <v>79</v>
       </c>
@@ -6499,7 +6514,7 @@
         <v>4105</v>
       </c>
     </row>
-    <row r="208" spans="6:9">
+    <row r="208" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F208" t="s">
         <v>156</v>
       </c>
@@ -6513,7 +6528,7 @@
         <v>4108</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F209" t="s">
         <v>21</v>
       </c>
@@ -6527,7 +6542,7 @@
         <v>4109</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F210" t="s">
         <v>45</v>
       </c>
@@ -6541,7 +6556,7 @@
         <v>4114</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F211" t="s">
         <v>82</v>
       </c>
@@ -6555,7 +6570,7 @@
         <v>4128</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A212">
         <v>15017</v>
       </c>
@@ -6578,7 +6593,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F213" t="s">
         <v>29</v>
       </c>
@@ -6592,7 +6607,7 @@
         <v>4132</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F214" t="s">
         <v>82</v>
       </c>
@@ -6606,7 +6621,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F215" t="s">
         <v>144</v>
       </c>
@@ -6620,7 +6635,7 @@
         <v>4150</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F216" t="s">
         <v>38</v>
       </c>
@@ -6634,7 +6649,7 @@
         <v>4155</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F217" t="s">
         <v>82</v>
       </c>
@@ -6648,7 +6663,7 @@
         <v>4162</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F218" t="s">
         <v>56</v>
       </c>
@@ -6662,7 +6677,7 @@
         <v>4163</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F219" t="s">
         <v>38</v>
       </c>
@@ -6676,7 +6691,7 @@
         <v>4167</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F220" t="s">
         <v>63</v>
       </c>
@@ -6690,7 +6705,7 @@
         <v>4171</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F221" t="s">
         <v>144</v>
       </c>
@@ -6704,7 +6719,7 @@
         <v>4172</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F222" t="s">
         <v>45</v>
       </c>
@@ -6718,7 +6733,7 @@
         <v>4173</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F223" t="s">
         <v>29</v>
       </c>
@@ -6732,7 +6747,7 @@
         <v>4510</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F224" t="s">
         <v>56</v>
       </c>
@@ -6746,7 +6761,7 @@
         <v>4523</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F225" t="s">
         <v>24</v>
       </c>
@@ -6760,7 +6775,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F226" t="s">
         <v>38</v>
       </c>
@@ -6774,7 +6789,7 @@
         <v>4533</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F227" t="s">
         <v>38</v>
       </c>
@@ -6788,7 +6803,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F228" t="s">
         <v>179</v>
       </c>
@@ -6802,7 +6817,7 @@
         <v>4552</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F229" t="s">
         <v>144</v>
       </c>
@@ -6816,7 +6831,7 @@
         <v>4557</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F230" t="s">
         <v>38</v>
       </c>
@@ -6830,7 +6845,7 @@
         <v>4566</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F231" t="s">
         <v>24</v>
       </c>
@@ -6844,7 +6859,7 @@
         <v>4716</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F232" t="s">
         <v>18</v>
       </c>
@@ -6858,7 +6873,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F233" t="s">
         <v>182</v>
       </c>
@@ -6872,7 +6887,7 @@
         <v>4739</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F234" t="s">
         <v>156</v>
       </c>
@@ -6886,7 +6901,7 @@
         <v>4743</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F235" t="s">
         <v>51</v>
       </c>
@@ -6900,7 +6915,7 @@
         <v>4747</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F236" t="s">
         <v>38</v>
       </c>
@@ -6914,7 +6929,7 @@
         <v>4749</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A237">
         <v>15021</v>
       </c>
@@ -6937,7 +6952,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F238" t="s">
         <v>82</v>
       </c>
@@ -6951,7 +6966,7 @@
         <v>4906</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F239" t="s">
         <v>187</v>
       </c>
@@ -6965,7 +6980,7 @@
         <v>4912</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F240" t="s">
         <v>136</v>
       </c>
@@ -6979,7 +6994,7 @@
         <v>4916</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A241">
         <v>15018</v>
       </c>
@@ -7002,7 +7017,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F242" t="s">
         <v>38</v>
       </c>
@@ -7016,7 +7031,7 @@
         <v>4931</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F243" t="s">
         <v>18</v>
       </c>
@@ -7030,7 +7045,7 @@
         <v>4934</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F244" t="s">
         <v>144</v>
       </c>
@@ -7044,7 +7059,7 @@
         <v>4939</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F245" t="s">
         <v>136</v>
       </c>
@@ -7058,7 +7073,7 @@
         <v>4945</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F246" t="s">
         <v>212</v>
       </c>
@@ -7072,7 +7087,7 @@
         <v>4953</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F247" t="s">
         <v>124</v>
       </c>
@@ -7086,7 +7101,7 @@
         <v>4960</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F248" t="s">
         <v>18</v>
       </c>
@@ -7100,7 +7115,7 @@
         <v>4961</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F249" t="s">
         <v>136</v>
       </c>
@@ -7114,7 +7129,7 @@
         <v>4967</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F250" t="s">
         <v>29</v>
       </c>
@@ -7128,7 +7143,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F251" t="s">
         <v>144</v>
       </c>
@@ -7142,7 +7157,7 @@
         <v>4974</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F252" t="s">
         <v>156</v>
       </c>
@@ -7156,7 +7171,7 @@
         <v>4991</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F253" t="s">
         <v>117</v>
       </c>
@@ -7170,7 +7185,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F254" t="s">
         <v>45</v>
       </c>
@@ -7184,7 +7199,7 @@
         <v>5011</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F255" t="s">
         <v>187</v>
       </c>
@@ -7198,7 +7213,7 @@
         <v>5202</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F256" t="s">
         <v>99</v>
       </c>
@@ -7212,7 +7227,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F257" t="s">
         <v>187</v>
       </c>
@@ -7226,7 +7241,7 @@
         <v>5227</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F258" t="s">
         <v>187</v>
       </c>
@@ -7240,7 +7255,7 @@
         <v>5230</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F259" t="s">
         <v>18</v>
       </c>
@@ -7254,7 +7269,7 @@
         <v>5251</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F260" t="s">
         <v>48</v>
       </c>
@@ -7268,7 +7283,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F261" t="s">
         <v>156</v>
       </c>
@@ -7282,7 +7297,7 @@
         <v>5283</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F262" t="s">
         <v>144</v>
       </c>
@@ -7296,7 +7311,7 @@
         <v>5289</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A263">
         <v>15016</v>
       </c>
@@ -7319,7 +7334,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F264" t="s">
         <v>182</v>
       </c>
@@ -7333,7 +7348,7 @@
         <v>5317</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F265" t="s">
         <v>156</v>
       </c>
@@ -7347,7 +7362,7 @@
         <v>5328</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F266" t="s">
         <v>179</v>
       </c>
@@ -7361,7 +7376,7 @@
         <v>5346</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F267" t="s">
         <v>56</v>
       </c>
@@ -7375,7 +7390,7 @@
         <v>5351</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F268" t="s">
         <v>38</v>
       </c>
@@ -7389,7 +7404,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F269" t="s">
         <v>32</v>
       </c>
@@ -7403,7 +7418,7 @@
         <v>5371</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F270" t="s">
         <v>51</v>
       </c>
@@ -7417,7 +7432,7 @@
         <v>5386</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F271" t="s">
         <v>79</v>
       </c>
@@ -7431,7 +7446,7 @@
         <v>5438</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F272" t="s">
         <v>29</v>
       </c>
@@ -7445,7 +7460,7 @@
         <v>5439</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F273" t="s">
         <v>21</v>
       </c>
@@ -7459,7 +7474,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F274" t="s">
         <v>45</v>
       </c>
@@ -7473,7 +7488,7 @@
         <v>5452</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F275" t="s">
         <v>32</v>
       </c>
@@ -7487,7 +7502,7 @@
         <v>5478</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F276" t="s">
         <v>82</v>
       </c>
@@ -7501,7 +7516,7 @@
         <v>5483</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F277" t="s">
         <v>18</v>
       </c>
@@ -7515,7 +7530,7 @@
         <v>5490</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F278" t="s">
         <v>16</v>
       </c>
@@ -7529,7 +7544,7 @@
         <v>5498</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F279" t="s">
         <v>45</v>
       </c>
@@ -7543,7 +7558,7 @@
         <v>5515</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F280" t="s">
         <v>136</v>
       </c>
@@ -7557,7 +7572,7 @@
         <v>5536</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F281" t="s">
         <v>179</v>
       </c>
@@ -7571,7 +7586,7 @@
         <v>5603</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F282" t="s">
         <v>45</v>
       </c>
@@ -7585,7 +7600,7 @@
         <v>5701</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F283" t="s">
         <v>198</v>
       </c>
@@ -7599,7 +7614,7 @@
         <v>5706</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F284" t="s">
         <v>51</v>
       </c>
@@ -7613,7 +7628,7 @@
         <v>6005</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F285" t="s">
         <v>156</v>
       </c>
@@ -7627,7 +7642,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F286" t="s">
         <v>182</v>
       </c>
@@ -7641,7 +7656,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A287">
         <v>15020</v>
       </c>
@@ -7664,7 +7679,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F288" t="s">
         <v>51</v>
       </c>
@@ -7678,7 +7693,7 @@
         <v>6104</v>
       </c>
     </row>
-    <row r="289" spans="6:9">
+    <row r="289" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F289" t="s">
         <v>144</v>
       </c>
@@ -7692,7 +7707,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="290" spans="6:9">
+    <row r="290" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F290" t="s">
         <v>79</v>
       </c>
@@ -7706,7 +7721,7 @@
         <v>6111</v>
       </c>
     </row>
-    <row r="291" spans="6:9">
+    <row r="291" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F291" t="s">
         <v>124</v>
       </c>
@@ -7720,7 +7735,7 @@
         <v>6116</v>
       </c>
     </row>
-    <row r="292" spans="6:9">
+    <row r="292" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F292" t="s">
         <v>38</v>
       </c>
@@ -7734,7 +7749,7 @@
         <v>6126</v>
       </c>
     </row>
-    <row r="293" spans="6:9">
+    <row r="293" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F293" t="s">
         <v>237</v>
       </c>
@@ -7748,7 +7763,7 @@
         <v>6129</v>
       </c>
     </row>
-    <row r="294" spans="6:9">
+    <row r="294" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F294" t="s">
         <v>136</v>
       </c>
@@ -7762,7 +7777,7 @@
         <v>6130</v>
       </c>
     </row>
-    <row r="295" spans="6:9">
+    <row r="295" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F295" t="s">
         <v>112</v>
       </c>
@@ -7776,7 +7791,7 @@
         <v>6136</v>
       </c>
     </row>
-    <row r="296" spans="6:9">
+    <row r="296" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F296" t="s">
         <v>144</v>
       </c>
@@ -7790,7 +7805,7 @@
         <v>6142</v>
       </c>
     </row>
-    <row r="297" spans="6:9">
+    <row r="297" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F297" t="s">
         <v>32</v>
       </c>
@@ -7804,7 +7819,7 @@
         <v>6143</v>
       </c>
     </row>
-    <row r="298" spans="6:9">
+    <row r="298" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F298" t="s">
         <v>51</v>
       </c>
@@ -7818,7 +7833,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="299" spans="6:9">
+    <row r="299" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F299" t="s">
         <v>21</v>
       </c>
@@ -7832,7 +7847,7 @@
         <v>6151</v>
       </c>
     </row>
-    <row r="300" spans="6:9">
+    <row r="300" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F300" t="s">
         <v>408</v>
       </c>
@@ -7846,7 +7861,7 @@
         <v>6152</v>
       </c>
     </row>
-    <row r="301" spans="6:9">
+    <row r="301" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F301" t="s">
         <v>45</v>
       </c>
@@ -7860,7 +7875,7 @@
         <v>6153</v>
       </c>
     </row>
-    <row r="302" spans="6:9">
+    <row r="302" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F302" t="s">
         <v>156</v>
       </c>
@@ -7874,7 +7889,7 @@
         <v>6158</v>
       </c>
     </row>
-    <row r="303" spans="6:9">
+    <row r="303" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F303" t="s">
         <v>156</v>
       </c>
@@ -7888,7 +7903,7 @@
         <v>6164</v>
       </c>
     </row>
-    <row r="304" spans="6:9">
+    <row r="304" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F304" t="s">
         <v>18</v>
       </c>
@@ -7902,7 +7917,7 @@
         <v>6170</v>
       </c>
     </row>
-    <row r="305" spans="6:9">
+    <row r="305" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F305" t="s">
         <v>56</v>
       </c>
@@ -7916,7 +7931,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="306" spans="6:9">
+    <row r="306" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F306" t="s">
         <v>35</v>
       </c>
@@ -7930,7 +7945,7 @@
         <v>6188</v>
       </c>
     </row>
-    <row r="307" spans="6:9">
+    <row r="307" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F307" t="s">
         <v>198</v>
       </c>
@@ -7944,7 +7959,7 @@
         <v>6189</v>
       </c>
     </row>
-    <row r="308" spans="6:9">
+    <row r="308" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F308" t="s">
         <v>45</v>
       </c>
@@ -7958,7 +7973,7 @@
         <v>6191</v>
       </c>
     </row>
-    <row r="309" spans="6:9">
+    <row r="309" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F309" t="s">
         <v>21</v>
       </c>
@@ -7972,7 +7987,7 @@
         <v>6197</v>
       </c>
     </row>
-    <row r="310" spans="6:9">
+    <row r="310" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F310" t="s">
         <v>136</v>
       </c>
@@ -7986,7 +8001,7 @@
         <v>6202</v>
       </c>
     </row>
-    <row r="311" spans="6:9">
+    <row r="311" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F311" t="s">
         <v>669</v>
       </c>
@@ -8000,7 +8015,7 @@
         <v>6204</v>
       </c>
     </row>
-    <row r="312" spans="6:9">
+    <row r="312" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F312" t="s">
         <v>45</v>
       </c>
@@ -8014,7 +8029,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="313" spans="6:9">
+    <row r="313" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F313" t="s">
         <v>21</v>
       </c>
@@ -8028,7 +8043,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="314" spans="6:9">
+    <row r="314" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F314" t="s">
         <v>156</v>
       </c>
@@ -8042,7 +8057,7 @@
         <v>6215</v>
       </c>
     </row>
-    <row r="315" spans="6:9">
+    <row r="315" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F315" t="s">
         <v>32</v>
       </c>
@@ -8056,7 +8071,7 @@
         <v>6217</v>
       </c>
     </row>
-    <row r="316" spans="6:9">
+    <row r="316" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F316" t="s">
         <v>680</v>
       </c>
@@ -8070,7 +8085,7 @@
         <v>6223</v>
       </c>
     </row>
-    <row r="317" spans="6:9">
+    <row r="317" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F317" t="s">
         <v>45</v>
       </c>
@@ -8084,7 +8099,7 @@
         <v>6224</v>
       </c>
     </row>
-    <row r="318" spans="6:9">
+    <row r="318" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F318" t="s">
         <v>212</v>
       </c>
@@ -8098,7 +8113,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="319" spans="6:9">
+    <row r="319" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F319" t="s">
         <v>156</v>
       </c>
@@ -8112,7 +8127,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="320" spans="6:9">
+    <row r="320" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F320" t="s">
         <v>48</v>
       </c>
@@ -8126,7 +8141,7 @@
         <v>6237</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A321">
         <v>15023</v>
       </c>
@@ -8149,7 +8164,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F322" t="s">
         <v>694</v>
       </c>
@@ -8163,7 +8178,7 @@
         <v>6248</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F323" t="s">
         <v>38</v>
       </c>
@@ -8177,7 +8192,7 @@
         <v>6257</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F324" t="s">
         <v>18</v>
       </c>
@@ -8191,7 +8206,7 @@
         <v>6266</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F325" t="s">
         <v>18</v>
       </c>
@@ -8205,7 +8220,7 @@
         <v>6269</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F326" t="s">
         <v>18</v>
       </c>
@@ -8219,7 +8234,7 @@
         <v>6274</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F327" t="s">
         <v>144</v>
       </c>
@@ -8233,7 +8248,7 @@
         <v>6275</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F328" t="s">
         <v>182</v>
       </c>
@@ -8247,7 +8262,7 @@
         <v>6282</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F329" t="s">
         <v>187</v>
       </c>
@@ -8261,7 +8276,7 @@
         <v>6288</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F330" t="s">
         <v>51</v>
       </c>
@@ -8275,7 +8290,7 @@
         <v>6403</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F331" t="s">
         <v>45</v>
       </c>
@@ -8289,7 +8304,7 @@
         <v>6411</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F332" t="s">
         <v>117</v>
       </c>
@@ -8303,7 +8318,7 @@
         <v>6416</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F333" t="s">
         <v>38</v>
       </c>
@@ -8317,7 +8332,7 @@
         <v>6438</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F334" t="s">
         <v>144</v>
       </c>
@@ -8331,7 +8346,7 @@
         <v>6443</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F335" t="s">
         <v>669</v>
       </c>
@@ -8345,7 +8360,7 @@
         <v>6477</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F336" t="s">
         <v>56</v>
       </c>
@@ -8359,7 +8374,7 @@
         <v>6483</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F337" t="s">
         <v>156</v>
       </c>
@@ -8373,7 +8388,7 @@
         <v>6486</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F338" t="s">
         <v>21</v>
       </c>
@@ -8387,7 +8402,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F339" t="s">
         <v>408</v>
       </c>
@@ -8401,7 +8416,7 @@
         <v>6517</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F340" t="s">
         <v>124</v>
       </c>
@@ -8415,7 +8430,7 @@
         <v>6530</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F341" t="s">
         <v>124</v>
       </c>
@@ -8429,7 +8444,7 @@
         <v>6538</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F342" t="s">
         <v>79</v>
       </c>
@@ -8443,7 +8458,7 @@
         <v>6578</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F343" t="s">
         <v>79</v>
       </c>
@@ -8457,7 +8472,7 @@
         <v>6591</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F344" t="s">
         <v>156</v>
       </c>
@@ -8471,7 +8486,7 @@
         <v>6657</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F345" t="s">
         <v>56</v>
       </c>
@@ -8485,7 +8500,7 @@
         <v>6683</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F346" t="s">
         <v>56</v>
       </c>
@@ -8499,7 +8514,7 @@
         <v>6683</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F347" t="s">
         <v>38</v>
       </c>
@@ -8513,7 +8528,7 @@
         <v>6698</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F348" t="s">
         <v>32</v>
       </c>
@@ -8527,7 +8542,7 @@
         <v>6742</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F349" t="s">
         <v>212</v>
       </c>
@@ -8541,7 +8556,7 @@
         <v>6761</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A350">
         <v>15015</v>
       </c>
@@ -8564,7 +8579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F351" t="s">
         <v>156</v>
       </c>
@@ -8578,7 +8593,7 @@
         <v>6788</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F352" t="s">
         <v>56</v>
       </c>
@@ -8592,7 +8607,7 @@
         <v>6797</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F353" t="s">
         <v>187</v>
       </c>
@@ -8606,7 +8621,7 @@
         <v>6799</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F354" t="s">
         <v>21</v>
       </c>
@@ -8620,7 +8635,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F355" t="s">
         <v>18</v>
       </c>
@@ -8634,7 +8649,7 @@
         <v>8027</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F356" t="s">
         <v>136</v>
       </c>
@@ -8648,7 +8663,7 @@
         <v>8028</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F357" t="s">
         <v>35</v>
       </c>
@@ -8662,7 +8677,7 @@
         <v>8032</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F358" t="s">
         <v>179</v>
       </c>
@@ -8676,7 +8691,7 @@
         <v>8033</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F359" t="s">
         <v>63</v>
       </c>
@@ -8690,7 +8705,7 @@
         <v>8034</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F360" t="s">
         <v>51</v>
       </c>
@@ -8704,7 +8719,7 @@
         <v>8038</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F361" t="s">
         <v>18</v>
       </c>
@@ -8718,7 +8733,7 @@
         <v>8039</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F362" t="s">
         <v>21</v>
       </c>
@@ -8732,7 +8747,7 @@
         <v>8040</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F363" t="s">
         <v>79</v>
       </c>
@@ -8746,7 +8761,7 @@
         <v>8064</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F364" t="s">
         <v>179</v>
       </c>
@@ -8760,7 +8775,7 @@
         <v>8066</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A365">
         <v>15019</v>
       </c>
@@ -8783,7 +8798,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F366" t="s">
         <v>680</v>
       </c>
@@ -8797,7 +8812,7 @@
         <v>8076</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F367" t="s">
         <v>112</v>
       </c>
@@ -8811,7 +8826,7 @@
         <v>8085</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F368" t="s">
         <v>156</v>
       </c>
@@ -8825,7 +8840,7 @@
         <v>8086</v>
       </c>
     </row>
-    <row r="369" spans="6:9">
+    <row r="369" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F369" t="s">
         <v>187</v>
       </c>
@@ -8839,7 +8854,7 @@
         <v>8087</v>
       </c>
     </row>
-    <row r="370" spans="6:9">
+    <row r="370" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F370" t="s">
         <v>24</v>
       </c>
@@ -8853,7 +8868,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="371" spans="6:9">
+    <row r="371" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F371" t="s">
         <v>48</v>
       </c>
@@ -8867,7 +8882,7 @@
         <v>8103</v>
       </c>
     </row>
-    <row r="372" spans="6:9">
+    <row r="372" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F372" t="s">
         <v>35</v>
       </c>
@@ -8881,7 +8896,7 @@
         <v>8119</v>
       </c>
     </row>
-    <row r="373" spans="6:9">
+    <row r="373" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F373" t="s">
         <v>141</v>
       </c>
@@ -8895,7 +8910,7 @@
         <v>8150</v>
       </c>
     </row>
-    <row r="374" spans="6:9">
+    <row r="374" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F374" t="s">
         <v>82</v>
       </c>
@@ -8909,7 +8924,7 @@
         <v>8176</v>
       </c>
     </row>
-    <row r="375" spans="6:9">
+    <row r="375" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F375" t="s">
         <v>45</v>
       </c>
@@ -8923,7 +8938,7 @@
         <v>8183</v>
       </c>
     </row>
-    <row r="376" spans="6:9">
+    <row r="376" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F376" t="s">
         <v>82</v>
       </c>
@@ -8937,7 +8952,7 @@
         <v>8213</v>
       </c>
     </row>
-    <row r="377" spans="6:9">
+    <row r="377" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F377" t="s">
         <v>408</v>
       </c>
@@ -8951,7 +8966,7 @@
         <v>8222</v>
       </c>
     </row>
-    <row r="378" spans="6:9">
+    <row r="378" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F378" t="s">
         <v>21</v>
       </c>
@@ -8965,7 +8980,7 @@
         <v>8227</v>
       </c>
     </row>
-    <row r="379" spans="6:9">
+    <row r="379" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F379" t="s">
         <v>156</v>
       </c>
@@ -8979,7 +8994,7 @@
         <v>8240</v>
       </c>
     </row>
-    <row r="380" spans="6:9">
+    <row r="380" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F380" t="s">
         <v>187</v>
       </c>
@@ -8993,7 +9008,7 @@
         <v>8249</v>
       </c>
     </row>
-    <row r="381" spans="6:9">
+    <row r="381" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F381" t="s">
         <v>198</v>
       </c>
@@ -9007,7 +9022,7 @@
         <v>8261</v>
       </c>
     </row>
-    <row r="382" spans="6:9">
+    <row r="382" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F382" t="s">
         <v>38</v>
       </c>
@@ -9021,7 +9036,7 @@
         <v>8277</v>
       </c>
     </row>
-    <row r="383" spans="6:9">
+    <row r="383" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F383" t="s">
         <v>18</v>
       </c>
@@ -9035,7 +9050,7 @@
         <v>8289</v>
       </c>
     </row>
-    <row r="384" spans="6:9">
+    <row r="384" spans="6:9" x14ac:dyDescent="0.4">
       <c r="F384" t="s">
         <v>51</v>
       </c>
@@ -9049,7 +9064,7 @@
         <v>8299</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F385" t="s">
         <v>51</v>
       </c>
@@ -9063,7 +9078,7 @@
         <v>8383</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F386" t="s">
         <v>45</v>
       </c>
@@ -9077,7 +9092,7 @@
         <v>8390</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F387" t="s">
         <v>38</v>
       </c>
@@ -9091,7 +9106,7 @@
         <v>8409</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A388">
         <v>15022</v>
       </c>
@@ -9114,7 +9129,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F389" t="s">
         <v>35</v>
       </c>
@@ -9128,7 +9143,7 @@
         <v>8916</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F390" t="s">
         <v>79</v>
       </c>
@@ -9142,7 +9157,7 @@
         <v>8924</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F391" t="s">
         <v>99</v>
       </c>
@@ -9156,7 +9171,7 @@
         <v>8927</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F392" t="s">
         <v>99</v>
       </c>
@@ -9170,7 +9185,7 @@
         <v>8935</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F393" t="s">
         <v>35</v>
       </c>
@@ -9184,7 +9199,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F394" t="s">
         <v>136</v>
       </c>
@@ -9198,7 +9213,7 @@
         <v>8942</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F395" t="s">
         <v>680</v>
       </c>
@@ -9212,7 +9227,7 @@
         <v>9912</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F396" t="s">
         <v>51</v>
       </c>
@@ -9226,7 +9241,7 @@
         <v>9935</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F397" t="s">
         <v>136</v>
       </c>
@@ -9240,7 +9255,7 @@
         <v>9958</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F398" t="s">
         <v>127</v>
       </c>

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python 封裝\封裝20260330\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578FB946-84E8-49E9-9528-FA7EBDD0873E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A60FEE7-EB09-4FDE-B87C-CF6E630A9F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{373C416E-3089-4CE1-B757-7C7D79C28350}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="848">
   <si>
     <t>序號</t>
   </si>
@@ -3690,8 +3690,8 @@
       <c r="I6">
         <v>1101</v>
       </c>
-      <c r="J6">
-        <v>123</v>
+      <c r="J6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.4">
@@ -3707,8 +3707,8 @@
       <c r="I7">
         <v>1103</v>
       </c>
-      <c r="J7">
-        <v>456</v>
+      <c r="J7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.4">
@@ -3724,8 +3724,8 @@
       <c r="I8">
         <v>1210</v>
       </c>
-      <c r="J8">
-        <v>789</v>
+      <c r="J8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python 封裝\封裝20260330\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A60FEE7-EB09-4FDE-B87C-CF6E630A9F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9299C287-5FFB-4A6F-93FF-147A501BB16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{373C416E-3089-4CE1-B757-7C7D79C28350}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="848">
   <si>
     <t>序號</t>
   </si>
@@ -3690,8 +3690,8 @@
       <c r="I6">
         <v>1101</v>
       </c>
-      <c r="J6" t="s">
-        <v>17</v>
+      <c r="J6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.4">
@@ -3707,8 +3707,8 @@
       <c r="I7">
         <v>1103</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
+      <c r="J7">
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.4">
@@ -3724,8 +3724,8 @@
       <c r="I8">
         <v>1210</v>
       </c>
-      <c r="J8" t="s">
-        <v>15</v>
+      <c r="J8">
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason Liao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191AD6D8-5741-42E3-99B7-38556B5389CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB33835-6D0D-4344-A854-28FE583BA27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3005,7 +3005,7 @@
         <v>1101</v>
       </c>
       <c r="J6" s="2">
-        <v>666</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3022,7 +3022,7 @@
         <v>1103</v>
       </c>
       <c r="J7" s="1">
-        <v>333</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3039,7 +3039,7 @@
         <v>1210</v>
       </c>
       <c r="J8" s="1">
-        <v>111</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason Liao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB33835-6D0D-4344-A854-28FE583BA27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE9997B-36E9-4796-B569-2093117EDCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3005,7 +3005,7 @@
         <v>1101</v>
       </c>
       <c r="J6" s="2">
-        <v>111</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3022,7 +3022,7 @@
         <v>1103</v>
       </c>
       <c r="J7" s="1">
-        <v>222</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3039,7 +3039,7 @@
         <v>1210</v>
       </c>
       <c r="J8" s="1">
-        <v>333</v>
+        <v>999</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3054,6 +3054,9 @@
       </c>
       <c r="I9" s="1">
         <v>1309</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason Liao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE9997B-36E9-4796-B569-2093117EDCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C6C3F-A356-4E5B-80B0-3412CAC4A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3005,7 +3005,7 @@
         <v>1101</v>
       </c>
       <c r="J6" s="2">
-        <v>777</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3022,7 +3022,7 @@
         <v>1103</v>
       </c>
       <c r="J7" s="1">
-        <v>888</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3039,7 +3039,7 @@
         <v>1210</v>
       </c>
       <c r="J8" s="1">
-        <v>999</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jason Liao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9C6C3F-A356-4E5B-80B0-3412CAC4A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B974D89F-751C-49BA-A5D7-C3A54BA5E8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-106" yWindow="-106" windowWidth="34136" windowHeight="18570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3005,7 +3005,7 @@
         <v>1101</v>
       </c>
       <c r="J6" s="2">
-        <v>555</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3022,7 +3022,7 @@
         <v>1103</v>
       </c>
       <c r="J7" s="1">
-        <v>333</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3039,7 +3039,7 @@
         <v>1210</v>
       </c>
       <c r="J8" s="1">
-        <v>111</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.8" customHeight="1" x14ac:dyDescent="0.4">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -11148,7 +11148,11 @@
           <t>8074</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr"/>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>電⽊梳1⽀</t>
+        </is>
+      </c>
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">

--- a/股東大會贈品.xlsx
+++ b/股東大會贈品.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>序號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>停止徵求</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>停止轉代</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>兌換停止</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>英文縮寫</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>公司簡稱</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>公司全名</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>股票代碼</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>紀念品</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>徵求型態</t>
         </is>
